--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-antecedent-familial-observe.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-antecedent-familial-observe.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3388" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3388" uniqueCount="345">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -844,6 +844,10 @@
     <t>ED.thumbnail</t>
   </si>
   <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
+  </si>
+  <si>
     <t>Observation.statusCode</t>
   </si>
   <si>
@@ -925,8 +929,8 @@
     <t>Observation.value</t>
   </si>
   <si>
-    <t>http://hl7.org/cda/stds/core/StructureDefinition/ANY
-http://hl7.org/cda/stds/core/StructureDefinition/BLhttp://hl7.org/cda/stds/core/StructureDefinition/EDhttp://hl7.org/cda/stds/core/StructureDefinition/SThttp://hl7.org/cda/stds/core/StructureDefinition/CDhttp://hl7.org/cda/stds/core/StructureDefinition/CVhttp://hl7.org/cda/stds/core/StructureDefinition/CEhttp://hl7.org/cda/stds/core/StructureDefinition/COhttp://hl7.org/cda/stds/core/StructureDefinition/SChttp://hl7.org/cda/stds/core/StructureDefinition/IIhttp://hl7.org/cda/stds/core/StructureDefinition/TELhttp://hl7.org/cda/stds/core/StructureDefinition/ADhttp://hl7.org/cda/stds/core/StructureDefinition/ENhttp://hl7.org/cda/stds/core/StructureDefinition/INThttp://hl7.org/cda/stds/core/StructureDefinition/REALhttp://hl7.org/cda/stds/core/StructureDefinition/PQhttp://hl7.org/cda/stds/core/StructureDefinition/MOhttp://hl7.org/cda/stds/core/StructureDefinition/TShttp://hl7.org/cda/stds/core/StructureDefinition/IVL-PQhttp://hl7.org/cda/stds/core/StructureDefinition/IVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/PIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/EIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/SXPR-TShttp://hl7.org/cda/stds/core/StructureDefinition/RTO-PQ-PQ</t>
+    <t>http://hl7.org/cda/stds/core/StructureDefinition/CD
+http://hl7.org/cda/stds/core/StructureDefinition/PQhttp://hl7.org/cda/stds/core/StructureDefinition/SThttp://hl7.org/cda/stds/core/StructureDefinition/ADhttp://hl7.org/cda/stds/core/StructureDefinition/BLhttp://hl7.org/cda/stds/core/StructureDefinition/CEhttp://hl7.org/cda/stds/core/StructureDefinition/COhttp://hl7.org/cda/stds/core/StructureDefinition/CShttp://hl7.org/cda/stds/core/StructureDefinition/CVhttp://hl7.org/cda/stds/core/StructureDefinition/EDhttp://hl7.org/cda/stds/core/StructureDefinition/ENhttp://hl7.org/cda/stds/core/StructureDefinition/IIhttp://hl7.org/cda/stds/core/StructureDefinition/INThttp://hl7.org/cda/stds/core/StructureDefinition/INT-POShttp://hl7.org/cda/stds/core/StructureDefinition/MOhttp://hl7.org/cda/stds/core/StructureDefinition/ONhttp://hl7.org/cda/stds/core/StructureDefinition/PNhttp://hl7.org/cda/stds/core/StructureDefinition/REALhttp://hl7.org/cda/stds/core/StructureDefinition/SChttp://hl7.org/cda/stds/core/StructureDefinition/TELhttp://hl7.org/cda/stds/core/StructureDefinition/TNhttp://hl7.org/cda/stds/core/StructureDefinition/TShttp://hl7.org/cda/stds/core/StructureDefinition/IVL-INThttp://hl7.org/cda/stds/core/StructureDefinition/IVL-PQhttp://hl7.org/cda/stds/core/StructureDefinition/IVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/PIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/EIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/SXPR-TShttp://hl7.org/cda/stds/core/StructureDefinition/RTO-PQ-PQ</t>
   </si>
   <si>
     <t>Observation.interpretationCode</t>
@@ -7976,7 +7980,7 @@
         <v>74</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>74</v>
+        <v>270</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>74</v>
@@ -7984,10 +7988,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8013,10 +8017,10 @@
         <v>91</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8047,7 +8051,7 @@
       </c>
       <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>74</v>
@@ -8065,7 +8069,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -8085,10 +8089,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8186,10 +8190,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8230,7 +8234,7 @@
         <v>74</v>
       </c>
       <c r="S67" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="T67" t="s" s="2">
         <v>74</v>
@@ -8289,10 +8293,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8392,10 +8396,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8495,10 +8499,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8598,10 +8602,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8701,10 +8705,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8802,10 +8806,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8903,10 +8907,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9006,10 +9010,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9109,10 +9113,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9212,10 +9216,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9238,13 +9242,13 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -9295,7 +9299,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9315,10 +9319,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9341,7 +9345,7 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
@@ -9374,7 +9378,7 @@
       </c>
       <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>74</v>
@@ -9392,7 +9396,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -9412,10 +9416,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9438,7 +9442,7 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
@@ -9491,7 +9495,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9511,10 +9515,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9570,25 +9574,25 @@
       </c>
       <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF80" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9608,10 +9612,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9634,7 +9638,7 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
@@ -9687,7 +9691,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -9707,10 +9711,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9733,13 +9737,13 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -9770,7 +9774,7 @@
       </c>
       <c r="Y82" s="2"/>
       <c r="Z82" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>74</v>
@@ -9788,7 +9792,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -9808,10 +9812,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9834,13 +9838,13 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -9871,7 +9875,7 @@
       </c>
       <c r="Y83" s="2"/>
       <c r="Z83" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>74</v>
@@ -9889,7 +9893,7 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -9909,10 +9913,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9938,10 +9942,10 @@
         <v>178</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -9992,7 +9996,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -10012,10 +10016,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10038,7 +10042,7 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
@@ -10091,7 +10095,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -10111,10 +10115,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10137,7 +10141,7 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
@@ -10190,7 +10194,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10210,10 +10214,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10236,7 +10240,7 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
@@ -10289,7 +10293,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10309,10 +10313,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10335,7 +10339,7 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
@@ -10388,7 +10392,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10408,10 +10412,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10434,7 +10438,7 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
@@ -10487,7 +10491,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10507,10 +10511,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10533,7 +10537,7 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
@@ -10586,7 +10590,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10606,10 +10610,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10632,7 +10636,7 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
@@ -10685,7 +10689,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10705,10 +10709,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10731,7 +10735,7 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
@@ -10784,7 +10788,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -10804,10 +10808,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10830,7 +10834,7 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -10883,7 +10887,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -10903,10 +10907,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -10929,7 +10933,7 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
@@ -10982,7 +10986,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -11002,10 +11006,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11028,11 +11032,11 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -11083,7 +11087,7 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -11103,10 +11107,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11204,10 +11208,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11305,10 +11309,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11406,10 +11410,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11507,10 +11511,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11610,10 +11614,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11713,10 +11717,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11816,10 +11820,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -11919,10 +11923,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12020,10 +12024,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12057,7 +12061,7 @@
       </c>
       <c r="Q105" s="2"/>
       <c r="R105" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="S105" t="s" s="2">
         <v>74</v>
@@ -12079,7 +12083,7 @@
       </c>
       <c r="Y105" s="2"/>
       <c r="Z105" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>74</v>
@@ -12097,7 +12101,7 @@
         <v>74</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -12117,10 +12121,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12143,7 +12147,7 @@
         <v>74</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L106" s="2"/>
       <c r="M106" s="2"/>
@@ -12196,7 +12200,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>75</v>
@@ -12216,10 +12220,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12242,7 +12246,7 @@
         <v>74</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L107" s="2"/>
       <c r="M107" s="2"/>
@@ -12295,7 +12299,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
